--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487136_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487136_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5735</v>
+        <v>2.9719</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3495</v>
+        <v>3.0515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.224</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.621</v>
+        <v>7.1731</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3104</v>
+        <v>3.5573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3106</v>
+        <v>3.6158</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1731</v>
+        <v>8.0274</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2952</v>
+        <v>4.9264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1221</v>
+        <v>3.101</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4479</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0152</v>
+        <v>-1.3691</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4327</v>
+        <v>0.5148</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5441</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R2" t="n">
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4647</v>
+        <v>-0.9201</v>
       </c>
       <c r="T2" t="n">
-        <v>1.051</v>
+        <v>-0.1507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4137</v>
+        <v>-0.7694</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4716</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>J. SAEZ PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0637</v>
+        <v>1.5674</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2504</v>
+        <v>2.5184</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1867</v>
+        <v>-0.951</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1731</v>
+        <v>2.1617</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5573</v>
+        <v>1.2906</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6158</v>
+        <v>0.8711</v>
       </c>
       <c r="J3" t="n">
-        <v>8.0274</v>
+        <v>3.4166</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9264</v>
+        <v>2.6597</v>
       </c>
       <c r="L3" t="n">
-        <v>3.101</v>
+        <v>0.7569</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-1.2549</v>
       </c>
       <c r="N3" t="n">
         <v>-1.3691</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5148</v>
+        <v>0.1142</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.2811</v>
+        <v>0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8252</v>
+        <v>-1.158</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8283</v>
+        <v>0.0968</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9518</v>
+        <v>0.3021</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.2053</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.2702</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAEZ PEREZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.955</v>
+        <v>1.3837</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7187</v>
+        <v>1.7486</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7637</v>
+        <v>-0.3649</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1617</v>
+        <v>-1.621</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2906</v>
+        <v>-1.3104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8711</v>
+        <v>-0.3106</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4166</v>
+        <v>-0.1731</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6597</v>
+        <v>-0.2952</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7569</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2549</v>
+        <v>-1.4479</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3691</v>
+        <v>-1.0152</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1142</v>
+        <v>-0.4327</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4845</v>
+        <v>0.275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5024</v>
+        <v>0.4502</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0179</v>
+        <v>-0.1752</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2702</v>
+        <v>1.1857</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0422</v>
+        <v>1.4716</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1247</v>
+        <v>0.1025</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6395</v>
+        <v>1.9385</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5148</v>
+        <v>-1.836</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1225</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6332</v>
+        <v>-0.389</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1105</v>
+        <v>0.4095</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4773</v>
+        <v>-0.7985</v>
       </c>
       <c r="V5" t="n">
         <v>1.228</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2319</v>
+        <v>-0.806</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2924</v>
+        <v>-0.8932</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0605</v>
+        <v>0.0872</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1249</v>
@@ -922,13 +922,13 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>0.507</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8593</v>
+        <v>0.2585</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3523</v>
+        <v>-0.3255</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2169</v>
+        <v>-1.21</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.444</v>
+        <v>-0.5442</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7729</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-2.178</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1362</v>
+        <v>-0.0291</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.082</v>
+        <v>-1.4116</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7409</v>
+        <v>-0.2902</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3411</v>
+        <v>-1.1214</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8184</v>
+        <v>-0.4497</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1851</v>
+        <v>-3.0366</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6333</v>
+        <v>2.5869</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8586</v>
+        <v>1.0186</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2317</v>
+        <v>-0.9265</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6269</v>
+        <v>1.945</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0402</v>
+        <v>-1.4683</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0466</v>
+        <v>-2.1102</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0064</v>
+        <v>0.6419</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.193</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1924</v>
+        <v>-0.9389</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3107</v>
+        <v>0.3355</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1183</v>
+        <v>-1.2744</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2336</v>
+        <v>-2.0483</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7909</v>
+        <v>-1.8411</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4427</v>
+        <v>-0.2072</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4497</v>
+        <v>-1.8184</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0366</v>
+        <v>-1.1851</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5869</v>
+        <v>-0.6333</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0186</v>
+        <v>-1.8586</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9265</v>
+        <v>-1.2317</v>
       </c>
       <c r="L9" t="n">
-        <v>1.945</v>
+        <v>-0.6269</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4683</v>
+        <v>0.0402</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1102</v>
+        <v>0.0466</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6419</v>
+        <v>-0.0064</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R9" t="n">
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7609</v>
+        <v>0.2261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>0.2105</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5956</v>
+        <v>0.0155</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9421</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4971</v>
+        <v>-2.2631</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3211</v>
+        <v>-0.221</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.176</v>
+        <v>-2.0422</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8579</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2531</v>
+        <v>-0.0192</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1322</v>
+        <v>0.2324</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3854</v>
+        <v>-0.2515</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6911</v>
+        <v>-5.5222</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0421</v>
+        <v>-1.1409</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.649</v>
+        <v>-4.3813</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9697</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3656</v>
+        <v>-0.1966</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>0.4254</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8897</v>
+        <v>-0.622</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3558</v>
@@ -1348,10 +1348,10 @@
         <v>-7.2357</v>
       </c>
       <c r="E12" t="n">
-        <v>4.326699999999999</v>
+        <v>4.326400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.5624</v>
+        <v>-11.5623</v>
       </c>
       <c r="G12" t="n">
         <v>-2.807300000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-1.5602</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.5803</v>
@@ -1390,13 +1390,13 @@
         <v>11.5804</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9301</v>
+        <v>-1.93</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5054</v>
+        <v>2.5055</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.4355</v>
+        <v>-4.4354</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4982</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2203</v>
+        <v>8.6675</v>
       </c>
       <c r="E13" t="n">
-        <v>8.3432</v>
+        <v>8.8439</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1229</v>
+        <v>-0.1765</v>
       </c>
       <c r="G13" t="n">
         <v>6.1848</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1924</v>
+        <v>-0.7453</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7139</v>
+        <v>-0.2131</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4786</v>
+        <v>-0.5321</v>
       </c>
       <c r="V13" t="n">
         <v>2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0426</v>
+        <v>5.607</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6455</v>
+        <v>5.3436</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3972</v>
+        <v>0.2633</v>
       </c>
       <c r="G14" t="n">
         <v>1.7996</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4939</v>
+        <v>1.0582</v>
       </c>
       <c r="T14" t="n">
-        <v>2.328</v>
+        <v>1.0262</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1659</v>
+        <v>0.032</v>
       </c>
       <c r="V14" t="n">
         <v>2.1701</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3053</v>
+        <v>2.108</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8567</v>
+        <v>3.4571</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4486</v>
+        <v>-1.3491</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6175</v>
+        <v>3.79</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2855</v>
+        <v>1.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.332</v>
+        <v>2.7219</v>
       </c>
       <c r="J15" t="n">
-        <v>2.186</v>
+        <v>4.544</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5677</v>
+        <v>1.4023</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6183999999999999</v>
+        <v>3.1417</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5685</v>
+        <v>-0.754</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2822</v>
+        <v>-0.3341</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2863</v>
+        <v>-0.4199</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7458</v>
+        <v>-0.4191</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9711</v>
+        <v>-0.0796</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7746</v>
+        <v>-0.3394</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3281</v>
+        <v>-1.842</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3704</v>
+        <v>-0.0422</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6985</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.527</v>
+        <v>2.0362</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9564</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4294</v>
+        <v>1.1809</v>
       </c>
       <c r="G16" t="n">
-        <v>3.79</v>
+        <v>0.6175</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0682</v>
+        <v>0.2855</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7219</v>
+        <v>0.332</v>
       </c>
       <c r="J16" t="n">
-        <v>4.544</v>
+        <v>2.186</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4023</v>
+        <v>1.5677</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1417</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.754</v>
+        <v>-1.5685</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3341</v>
+        <v>-1.2822</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4199</v>
+        <v>-0.2863</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0001</v>
+        <v>1.4767</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5803</v>
+        <v>0.9697</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4197</v>
+        <v>0.507</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.842</v>
+        <v>0.3281</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0422</v>
+        <v>-0.3704</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7997</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.383</v>
+        <v>1.1153</v>
       </c>
       <c r="E17" t="n">
         <v>0.5729</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8101</v>
+        <v>0.5424</v>
       </c>
       <c r="G17" t="n">
         <v>-0.666</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>1.47</v>
+        <v>1.2023</v>
       </c>
       <c r="T17" t="n">
         <v>0.9928</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4772</v>
+        <v>0.2095</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7268</v>
+        <v>0.7734</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2161</v>
+        <v>-0.116</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9429</v>
+        <v>0.8893</v>
       </c>
       <c r="G18" t="n">
         <v>0.7321</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1983</v>
+        <v>-0.1517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1586</v>
+        <v>0.1051</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3005</v>
+        <v>-0.2934</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7392</v>
+        <v>1.0382</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4387</v>
+        <v>-1.3316</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7841</v>
@@ -1936,13 +1936,13 @@
         <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2427</v>
+        <v>0.6488</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9116</v>
+        <v>1.2106</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.5619</v>
       </c>
       <c r="V19" t="n">
         <v>0.614</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.8343</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0916</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8696</v>
+        <v>-0.8428</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7861</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1752</v>
+        <v>-0.0483</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3744</v>
+        <v>-1.2475</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6243</v>
+        <v>-0.5242</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7501</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1252</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4422</v>
+        <v>-0.3153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3827</v>
+        <v>-0.3559</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4065</v>
+        <v>-2.0257</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8152</v>
+        <v>-1.5148</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5913</v>
+        <v>-0.511</v>
       </c>
       <c r="G22" t="n">
         <v>-1.45</v>
@@ -2170,13 +2170,13 @@
         <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3774</v>
+        <v>0.0033</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0727</v>
+        <v>0.3731</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4501</v>
+        <v>-0.3698</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8221</v>
+        <v>-2.5147</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7121</v>
+        <v>-2.5119</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.11</v>
+        <v>-0.0029</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9039</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5671</v>
+        <v>-0.2598</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3292</v>
+        <v>-0.2221</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7057</v>
+        <v>-6.156</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0923</v>
+        <v>-3.8906</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6135</v>
+        <v>-2.2655</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6012</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0696</v>
+        <v>-0.5199</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8328</v>
+        <v>0.3689</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2367</v>
+        <v>-0.8887</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.235599999999998</v>
+        <v>7.235800000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>11.5623</v>
+        <v>11.562</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3267</v>
+        <v>-4.3268</v>
       </c>
       <c r="G25" t="n">
         <v>2.807499999999999</v>
@@ -2404,13 +2404,13 @@
         <v>11.5804</v>
       </c>
       <c r="S25" t="n">
-        <v>1.930100000000001</v>
+        <v>1.9299</v>
       </c>
       <c r="T25" t="n">
-        <v>4.435300000000001</v>
+        <v>4.4355</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.5053</v>
+        <v>-2.5052</v>
       </c>
       <c r="V25" t="n">
         <v>2.4981</v>
